--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/202.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/202.xlsx
@@ -426,13 +426,13 @@
         <v>-3.6860929992375</v>
       </c>
       <c r="E2">
-        <v>-18.71887053549574</v>
+        <v>-16.24509198237764</v>
       </c>
       <c r="F2">
-        <v>-5.196858310961528</v>
+        <v>-4.320629496363073</v>
       </c>
       <c r="G2">
-        <v>-10.54199973901178</v>
+        <v>-9.49532110858811</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.676212750216932</v>
       </c>
       <c r="E3">
-        <v>-19.46895791317824</v>
+        <v>-17.24579416859263</v>
       </c>
       <c r="F3">
-        <v>-4.678615096422101</v>
+        <v>-4.391332310926816</v>
       </c>
       <c r="G3">
-        <v>-10.41519591322108</v>
+        <v>-10.29124577768523</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.675471162962408</v>
       </c>
       <c r="E4">
-        <v>-19.19084621047117</v>
+        <v>-18.08282824722241</v>
       </c>
       <c r="F4">
-        <v>-5.09966513522366</v>
+        <v>-4.203335985596274</v>
       </c>
       <c r="G4">
-        <v>-10.90386885081844</v>
+        <v>-9.741844192715478</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.680482809789352</v>
       </c>
       <c r="E5">
-        <v>-19.95230911486095</v>
+        <v>-17.80133377443161</v>
       </c>
       <c r="F5">
-        <v>-4.630030519880508</v>
+        <v>-3.789858881591109</v>
       </c>
       <c r="G5">
-        <v>-11.02618026631235</v>
+        <v>-9.645189505150917</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.686581531362609</v>
       </c>
       <c r="E6">
-        <v>-22.31182521181751</v>
+        <v>-18.76099440071509</v>
       </c>
       <c r="F6">
-        <v>-5.340845132916138</v>
+        <v>-4.213736966705825</v>
       </c>
       <c r="G6">
-        <v>-10.72459618877583</v>
+        <v>-9.398567104657371</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.681929024649374</v>
       </c>
       <c r="E7">
-        <v>-19.8969621055392</v>
+        <v>-20.16527871896767</v>
       </c>
       <c r="F7">
-        <v>-4.740209183024661</v>
+        <v>-4.063103324711151</v>
       </c>
       <c r="G7">
-        <v>-9.740890755600168</v>
+        <v>-9.83591334421387</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.655754757068672</v>
       </c>
       <c r="E8">
-        <v>-20.67518942070536</v>
+        <v>-21.15092372910717</v>
       </c>
       <c r="F8">
-        <v>-4.722418336314736</v>
+        <v>-3.985526717438978</v>
       </c>
       <c r="G8">
-        <v>-9.461950809552256</v>
+        <v>-9.021509209916539</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.593965175886577</v>
       </c>
       <c r="E9">
-        <v>-23.52252179471619</v>
+        <v>-22.12671930827997</v>
       </c>
       <c r="F9">
-        <v>-5.259834114391958</v>
+        <v>-3.951761633733467</v>
       </c>
       <c r="G9">
-        <v>-8.766736246305307</v>
+        <v>-8.791290562570081</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.478400454707079</v>
       </c>
       <c r="E10">
-        <v>-22.88103175221163</v>
+        <v>-22.64743042052596</v>
       </c>
       <c r="F10">
-        <v>-5.110586331062168</v>
+        <v>-4.140482780541459</v>
       </c>
       <c r="G10">
-        <v>-9.252813716199878</v>
+        <v>-8.721620131696119</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.296618129036017</v>
       </c>
       <c r="E11">
-        <v>-23.48325992506969</v>
+        <v>-21.93713474394885</v>
       </c>
       <c r="F11">
-        <v>-5.239499351388035</v>
+        <v>-3.805214328136803</v>
       </c>
       <c r="G11">
-        <v>-8.576734106169916</v>
+        <v>-8.426574381599654</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.039969378901377</v>
       </c>
       <c r="E12">
-        <v>-25.19538990636371</v>
+        <v>-22.65909124109571</v>
       </c>
       <c r="F12">
-        <v>-5.41626715657363</v>
+        <v>-4.040209734799982</v>
       </c>
       <c r="G12">
-        <v>-8.366137062234719</v>
+        <v>-7.877606478095548</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.701705730795697</v>
       </c>
       <c r="E13">
-        <v>-23.86649562339082</v>
+        <v>-24.30393262710975</v>
       </c>
       <c r="F13">
-        <v>-4.852220194863808</v>
+        <v>-3.554725965939066</v>
       </c>
       <c r="G13">
-        <v>-8.794438891377927</v>
+        <v>-7.735835675921798</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.287484607744898</v>
       </c>
       <c r="E14">
-        <v>-25.5260590784038</v>
+        <v>-24.35143631945021</v>
       </c>
       <c r="F14">
-        <v>-4.884051869051184</v>
+        <v>-3.406063009995653</v>
       </c>
       <c r="G14">
-        <v>-9.165349103052332</v>
+        <v>-7.100495639298108</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.805764738401189</v>
       </c>
       <c r="E15">
-        <v>-26.95435789431906</v>
+        <v>-25.72380848137075</v>
       </c>
       <c r="F15">
-        <v>-5.052248556720013</v>
+        <v>-3.536421531439406</v>
       </c>
       <c r="G15">
-        <v>-9.485048485779751</v>
+        <v>-6.336338965195836</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.265359668843414</v>
       </c>
       <c r="E16">
-        <v>-25.40089205683179</v>
+        <v>-24.43843736208558</v>
       </c>
       <c r="F16">
-        <v>-4.774312240630515</v>
+        <v>-3.706559912300396</v>
       </c>
       <c r="G16">
-        <v>-8.523805104088048</v>
+        <v>-6.004744792345816</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.682390898244821</v>
       </c>
       <c r="E17">
-        <v>-27.04679763423763</v>
+        <v>-26.6291998751463</v>
       </c>
       <c r="F17">
-        <v>-4.504652971629788</v>
+        <v>-3.187793997929803</v>
       </c>
       <c r="G17">
-        <v>-6.821304091789211</v>
+        <v>-6.739361468601171</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.07197824488919045</v>
       </c>
       <c r="E18">
-        <v>-28.66467648601001</v>
+        <v>-27.98841229160055</v>
       </c>
       <c r="F18">
-        <v>-4.655526011803871</v>
+        <v>-3.606426860649992</v>
       </c>
       <c r="G18">
-        <v>-5.920080900724495</v>
+        <v>-5.74208941980558</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.547977835006265</v>
       </c>
       <c r="E19">
-        <v>-28.34016603862035</v>
+        <v>-28.48797543023071</v>
       </c>
       <c r="F19">
-        <v>-3.935135471591878</v>
+        <v>-3.286684498476008</v>
       </c>
       <c r="G19">
-        <v>-7.220287729636635</v>
+        <v>-5.079927343222714</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.155111697581894</v>
       </c>
       <c r="E20">
-        <v>-29.38758849117248</v>
+        <v>-28.63573048015298</v>
       </c>
       <c r="F20">
-        <v>-4.273156588876036</v>
+        <v>-2.491470844238747</v>
       </c>
       <c r="G20">
-        <v>-6.765547883816806</v>
+        <v>-5.364405831957826</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.729861816258192</v>
       </c>
       <c r="E21">
-        <v>-31.20205292809183</v>
+        <v>-29.60600811374744</v>
       </c>
       <c r="F21">
-        <v>-4.600128941741654</v>
+        <v>-2.578114761101964</v>
       </c>
       <c r="G21">
-        <v>-8.275891590834187</v>
+        <v>-5.207598531944707</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.246375560281583</v>
       </c>
       <c r="E22">
-        <v>-28.60929777737021</v>
+        <v>-29.79870826819583</v>
       </c>
       <c r="F22">
-        <v>-3.884739255540361</v>
+        <v>-2.541597012516951</v>
       </c>
       <c r="G22">
-        <v>-6.033096304344134</v>
+        <v>-4.318736917923629</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.678984311141702</v>
       </c>
       <c r="E23">
-        <v>-29.47101430357879</v>
+        <v>-29.79652554372414</v>
       </c>
       <c r="F23">
-        <v>-3.614331970774908</v>
+        <v>-2.286619727363444</v>
       </c>
       <c r="G23">
-        <v>-5.606515958881346</v>
+        <v>-4.403020096807934</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.002805770781323</v>
       </c>
       <c r="E24">
-        <v>-30.44979188288564</v>
+        <v>-30.99813347928943</v>
       </c>
       <c r="F24">
-        <v>-4.207475337508063</v>
+        <v>-2.14724774020983</v>
       </c>
       <c r="G24">
-        <v>-5.932660973773725</v>
+        <v>-4.703240229582281</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.191263195440151</v>
       </c>
       <c r="E25">
-        <v>-30.88143923258577</v>
+        <v>-30.50046324279447</v>
       </c>
       <c r="F25">
-        <v>-3.662928144460141</v>
+        <v>-2.202770722117272</v>
       </c>
       <c r="G25">
-        <v>-6.544986097808403</v>
+        <v>-5.114939672846046</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.227793301425054</v>
       </c>
       <c r="E26">
-        <v>-28.71958876182702</v>
+        <v>-31.22757993607307</v>
       </c>
       <c r="F26">
-        <v>-3.518496489210227</v>
+        <v>-2.155821342828804</v>
       </c>
       <c r="G26">
-        <v>-7.103435403736981</v>
+        <v>-5.008906209768729</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>3.100627249156045</v>
       </c>
       <c r="E27">
-        <v>-31.22400697008102</v>
+        <v>-30.98212985214632</v>
       </c>
       <c r="F27">
-        <v>-3.237133217175348</v>
+        <v>-2.452992350011308</v>
       </c>
       <c r="G27">
-        <v>-7.03702917076474</v>
+        <v>-5.05178108504783</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.809546851677764</v>
       </c>
       <c r="E28">
-        <v>-30.73040556748195</v>
+        <v>-30.40621664174684</v>
       </c>
       <c r="F28">
-        <v>-3.265829520743128</v>
+        <v>-2.166390482521123</v>
       </c>
       <c r="G28">
-        <v>-6.60377807604032</v>
+        <v>-4.896831001082242</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.365747969207667</v>
       </c>
       <c r="E29">
-        <v>-29.02295576407486</v>
+        <v>-29.88485116500674</v>
       </c>
       <c r="F29">
-        <v>-3.478606456928417</v>
+        <v>-1.813341123815377</v>
       </c>
       <c r="G29">
-        <v>-6.938424571877547</v>
+        <v>-4.97147056081065</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.788292846842492</v>
       </c>
       <c r="E30">
-        <v>-29.8839386774942</v>
+        <v>-29.40757717544233</v>
       </c>
       <c r="F30">
-        <v>-3.587598897951762</v>
+        <v>-1.986266960986788</v>
       </c>
       <c r="G30">
-        <v>-5.708100048753883</v>
+        <v>-4.971490424083886</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.110124460734079</v>
       </c>
       <c r="E31">
-        <v>-29.47348911462398</v>
+        <v>-30.59572422201983</v>
       </c>
       <c r="F31">
-        <v>-3.143430781672876</v>
+        <v>-2.141878262704883</v>
       </c>
       <c r="G31">
-        <v>-6.667764300223353</v>
+        <v>-5.659881952974398</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.3672483320804781</v>
       </c>
       <c r="E32">
-        <v>-28.71343003717659</v>
+        <v>-28.74158808855628</v>
       </c>
       <c r="F32">
-        <v>-3.457937033493764</v>
+        <v>-2.058044996439365</v>
       </c>
       <c r="G32">
-        <v>-7.169957505803096</v>
+        <v>-5.876126787599591</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.3980468852459687</v>
       </c>
       <c r="E33">
-        <v>-27.93884361511259</v>
+        <v>-28.20230117593083</v>
       </c>
       <c r="F33">
-        <v>-3.009886359197956</v>
+        <v>-2.320068374721085</v>
       </c>
       <c r="G33">
-        <v>-8.121282493059143</v>
+        <v>-5.536762764368902</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.141220457044133</v>
       </c>
       <c r="E34">
-        <v>-29.2568922028371</v>
+        <v>-28.47981512006888</v>
       </c>
       <c r="F34">
-        <v>-3.480157989073861</v>
+        <v>-2.377620856765386</v>
       </c>
       <c r="G34">
-        <v>-8.163150962494305</v>
+        <v>-6.139725665618521</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.826228531780301</v>
       </c>
       <c r="E35">
-        <v>-27.23160465849066</v>
+        <v>-27.29269830132814</v>
       </c>
       <c r="F35">
-        <v>-2.848570919544183</v>
+        <v>-2.047340004492987</v>
       </c>
       <c r="G35">
-        <v>-7.524162704686338</v>
+        <v>-5.843468255854681</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.41786762189713</v>
       </c>
       <c r="E36">
-        <v>-25.81569121898638</v>
+        <v>-27.80321129010885</v>
       </c>
       <c r="F36">
-        <v>-2.876831501858091</v>
+        <v>-2.096873061710786</v>
       </c>
       <c r="G36">
-        <v>-7.81181931713915</v>
+        <v>-6.627858984292978</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.89260892131028</v>
       </c>
       <c r="E37">
-        <v>-27.25389833603042</v>
+        <v>-27.14077252684481</v>
       </c>
       <c r="F37">
-        <v>-3.309243427956447</v>
+        <v>-2.221845538301536</v>
       </c>
       <c r="G37">
-        <v>-8.312370492131414</v>
+        <v>-6.468582017307563</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.238487616787139</v>
       </c>
       <c r="E38">
-        <v>-25.60424771062023</v>
+        <v>-26.24644419506999</v>
       </c>
       <c r="F38">
-        <v>-3.146675496789642</v>
+        <v>-2.121152510286839</v>
       </c>
       <c r="G38">
-        <v>-8.302975163890963</v>
+        <v>-6.383222911122995</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.451500940012976</v>
       </c>
       <c r="E39">
-        <v>-25.68696028837033</v>
+        <v>-25.37938180529535</v>
       </c>
       <c r="F39">
-        <v>-2.994623689801375</v>
+        <v>-2.027807101134974</v>
       </c>
       <c r="G39">
-        <v>-8.044405004546187</v>
+        <v>-6.440760192595528</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.541055145381746</v>
       </c>
       <c r="E40">
-        <v>-24.6482189204909</v>
+        <v>-25.56825992768128</v>
       </c>
       <c r="F40">
-        <v>-3.569874320634061</v>
+        <v>-2.054606443350344</v>
       </c>
       <c r="G40">
-        <v>-8.199434541604719</v>
+        <v>-6.10634212440051</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.52411612809963</v>
       </c>
       <c r="E41">
-        <v>-24.97757483506877</v>
+        <v>-24.43429380836856</v>
       </c>
       <c r="F41">
-        <v>-2.286375358979618</v>
+        <v>-1.796832589844985</v>
       </c>
       <c r="G41">
-        <v>-8.01296144301419</v>
+        <v>-7.147319995405559</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.422153229421227</v>
       </c>
       <c r="E42">
-        <v>-25.15607822350312</v>
+        <v>-22.15616344627784</v>
       </c>
       <c r="F42">
-        <v>-2.97453660865089</v>
+        <v>-2.262766059632429</v>
       </c>
       <c r="G42">
-        <v>-9.157609047581516</v>
+        <v>-6.732204069145267</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.262844279632583</v>
       </c>
       <c r="E43">
-        <v>-22.99328809438777</v>
+        <v>-24.3230337304741</v>
       </c>
       <c r="F43">
-        <v>-3.23027516344757</v>
+        <v>-2.076252511952898</v>
       </c>
       <c r="G43">
-        <v>-8.091427993385995</v>
+        <v>-6.559526013816882</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.073951355390847</v>
       </c>
       <c r="E44">
-        <v>-22.18155007156485</v>
+        <v>-23.61168744792722</v>
       </c>
       <c r="F44">
-        <v>-2.747034613513437</v>
+        <v>-1.881174473695823</v>
       </c>
       <c r="G44">
-        <v>-9.540314733012345</v>
+        <v>-7.154808449415391</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.87872808703194</v>
       </c>
       <c r="E45">
-        <v>-21.57058647234599</v>
+        <v>-22.1481661611803</v>
       </c>
       <c r="F45">
-        <v>-2.903587768968515</v>
+        <v>-2.071803350632462</v>
       </c>
       <c r="G45">
-        <v>-9.227345689366263</v>
+        <v>-6.892295430333343</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.700881723849875</v>
       </c>
       <c r="E46">
-        <v>-20.02414429804462</v>
+        <v>-21.79030803119816</v>
       </c>
       <c r="F46">
-        <v>-3.595005330900193</v>
+        <v>-1.934972794670637</v>
       </c>
       <c r="G46">
-        <v>-9.700498789475519</v>
+        <v>-7.442614036417471</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.558859237976044</v>
       </c>
       <c r="E47">
-        <v>-21.36307367941851</v>
+        <v>-20.6941637267975</v>
       </c>
       <c r="F47">
-        <v>-2.185587897081002</v>
+        <v>-1.958892731793875</v>
       </c>
       <c r="G47">
-        <v>-9.997216365069319</v>
+        <v>-7.576840105307221</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.462184390880374</v>
       </c>
       <c r="E48">
-        <v>-19.6042506026314</v>
+        <v>-21.54492813861853</v>
       </c>
       <c r="F48">
-        <v>-3.250150182542939</v>
+        <v>-1.71678164914065</v>
       </c>
       <c r="G48">
-        <v>-8.953679442362411</v>
+        <v>-7.585831546991882</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.420252046498261</v>
       </c>
       <c r="E49">
-        <v>-20.77365655952815</v>
+        <v>-20.01581190587051</v>
       </c>
       <c r="F49">
-        <v>-2.925592520656481</v>
+        <v>-1.832901363297681</v>
       </c>
       <c r="G49">
-        <v>-9.423260463834794</v>
+        <v>-7.755295062601634</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.43339746048271</v>
       </c>
       <c r="E50">
-        <v>-19.36098097893935</v>
+        <v>-19.33447129209845</v>
       </c>
       <c r="F50">
-        <v>-3.267717370054108</v>
+        <v>-2.026364913486701</v>
       </c>
       <c r="G50">
-        <v>-8.768182954705969</v>
+        <v>-7.221549047487098</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.496174038331835</v>
       </c>
       <c r="E51">
-        <v>-19.41102967367212</v>
+        <v>-18.40001615214166</v>
       </c>
       <c r="F51">
-        <v>-2.476012680135105</v>
+        <v>-1.904002622582171</v>
       </c>
       <c r="G51">
-        <v>-9.140357794776374</v>
+        <v>-7.378399384592227</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.605944286640384</v>
       </c>
       <c r="E52">
-        <v>-17.47003967297846</v>
+        <v>-17.95820011405731</v>
       </c>
       <c r="F52">
-        <v>-2.758177811815896</v>
+        <v>-1.728169215826934</v>
       </c>
       <c r="G52">
-        <v>-11.79213456664245</v>
+        <v>-7.988450163841426</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.749592531705119</v>
       </c>
       <c r="E53">
-        <v>-17.34576928925997</v>
+        <v>-17.41391376612739</v>
       </c>
       <c r="F53">
-        <v>-3.208619154436183</v>
+        <v>-1.353646917305819</v>
       </c>
       <c r="G53">
-        <v>-9.338815068219064</v>
+        <v>-8.432000365738519</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.916242786772778</v>
       </c>
       <c r="E54">
-        <v>-17.5889664573679</v>
+        <v>-17.19204118212159</v>
       </c>
       <c r="F54">
-        <v>-3.476022778999086</v>
+        <v>-2.071669983480611</v>
       </c>
       <c r="G54">
-        <v>-9.399358325041256</v>
+        <v>-9.365438475445883</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.097005816845929</v>
       </c>
       <c r="E55">
-        <v>-16.71172858649803</v>
+        <v>-16.63467660125752</v>
       </c>
       <c r="F55">
-        <v>-1.947916035339379</v>
+        <v>-1.850933264921821</v>
       </c>
       <c r="G55">
-        <v>-10.26541028029676</v>
+        <v>-8.253217664435718</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.276586068764141</v>
       </c>
       <c r="E56">
-        <v>-16.21318435451959</v>
+        <v>-16.88634201575979</v>
       </c>
       <c r="F56">
-        <v>-2.545332121136174</v>
+        <v>-1.976025026418574</v>
       </c>
       <c r="G56">
-        <v>-10.9895557010114</v>
+        <v>-8.665695085901211</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.447628284432955</v>
       </c>
       <c r="E57">
-        <v>-16.53559358996969</v>
+        <v>-16.00678103772398</v>
       </c>
       <c r="F57">
-        <v>-3.144101759269143</v>
+        <v>-1.281931009408452</v>
       </c>
       <c r="G57">
-        <v>-11.40540325783587</v>
+        <v>-8.911754693653082</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.602325958965455</v>
       </c>
       <c r="E58">
-        <v>-14.80491497914026</v>
+        <v>-15.71247098349148</v>
       </c>
       <c r="F58">
-        <v>-1.974621772038232</v>
+        <v>-1.83673587600524</v>
       </c>
       <c r="G58">
-        <v>-11.72365924270816</v>
+        <v>-9.335875303780192</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.731638069516535</v>
       </c>
       <c r="E59">
-        <v>-14.69418926117871</v>
+        <v>-17.15286535348123</v>
       </c>
       <c r="F59">
-        <v>-2.733401342798162</v>
+        <v>-1.896046153678282</v>
       </c>
       <c r="G59">
-        <v>-10.25785561537614</v>
+        <v>-9.392770339418107</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.834594648604061</v>
       </c>
       <c r="E60">
-        <v>-15.47357586569084</v>
+        <v>-15.77168983808978</v>
       </c>
       <c r="F60">
-        <v>-2.354298172539566</v>
+        <v>-1.665895867954079</v>
       </c>
       <c r="G60">
-        <v>-10.44502061798437</v>
+        <v>-9.223853063822332</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.908091224400541</v>
       </c>
       <c r="E61">
-        <v>-15.7896452375302</v>
+        <v>-15.68771834456555</v>
       </c>
       <c r="F61">
-        <v>-2.085634601157005</v>
+        <v>-1.672128504292742</v>
       </c>
       <c r="G61">
-        <v>-11.77966705214155</v>
+        <v>-9.7425625810975</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.952634787885962</v>
       </c>
       <c r="E62">
-        <v>-14.27447217625179</v>
+        <v>-15.18271198017817</v>
       </c>
       <c r="F62">
-        <v>-3.10817297990752</v>
+        <v>-1.619292746239981</v>
       </c>
       <c r="G62">
-        <v>-12.16178346046639</v>
+        <v>-9.824246981733477</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.975085735129812</v>
       </c>
       <c r="E63">
-        <v>-15.03351234704746</v>
+        <v>-16.05127329484935</v>
       </c>
       <c r="F63">
-        <v>-2.800021134433507</v>
+        <v>-1.599846821459263</v>
       </c>
       <c r="G63">
-        <v>-11.57980610739021</v>
+        <v>-9.168192861670567</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.976343549425522</v>
       </c>
       <c r="E64">
-        <v>-14.24997313187029</v>
+        <v>-13.62319157294264</v>
       </c>
       <c r="F64">
-        <v>-2.454107332535476</v>
+        <v>-2.076946683836444</v>
       </c>
       <c r="G64">
-        <v>-10.64091883972521</v>
+        <v>-9.785189165461155</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.961502156116856</v>
       </c>
       <c r="E65">
-        <v>-16.06549270323343</v>
+        <v>-14.66894754705995</v>
       </c>
       <c r="F65">
-        <v>-2.548023486827869</v>
+        <v>-2.52616287106799</v>
       </c>
       <c r="G65">
-        <v>-11.31487307951896</v>
+        <v>-9.169315136608379</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.935483441015875</v>
       </c>
       <c r="E66">
-        <v>-13.41994913100439</v>
+        <v>-14.37977278235215</v>
       </c>
       <c r="F66">
-        <v>-2.881806676479305</v>
+        <v>-2.094602506659712</v>
       </c>
       <c r="G66">
-        <v>-10.8200127323087</v>
+        <v>-8.818079497073864</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.896631999791996</v>
       </c>
       <c r="E67">
-        <v>-14.44073962791741</v>
+        <v>-13.29720937150049</v>
       </c>
       <c r="F67">
-        <v>-3.257020661781758</v>
+        <v>-2.186905829618856</v>
       </c>
       <c r="G67">
-        <v>-10.27608016856983</v>
+        <v>-8.994415705223144</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.846431729500848</v>
       </c>
       <c r="E68">
-        <v>-13.59630602275911</v>
+        <v>-14.6770625724817</v>
       </c>
       <c r="F68">
-        <v>-3.695014127440177</v>
+        <v>-2.07032637155327</v>
       </c>
       <c r="G68">
-        <v>-11.32478816340907</v>
+        <v>-8.587202051165091</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.783205845208129</v>
       </c>
       <c r="E69">
-        <v>-14.1474258379666</v>
+        <v>-13.82760688964889</v>
       </c>
       <c r="F69">
-        <v>-2.59563058983416</v>
+        <v>-2.034302329940325</v>
       </c>
       <c r="G69">
-        <v>-11.74906436917653</v>
+        <v>-9.721620070016071</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.701031151429472</v>
       </c>
       <c r="E70">
-        <v>-14.55772369695756</v>
+        <v>-13.13816936435111</v>
       </c>
       <c r="F70">
-        <v>-2.724396989129732</v>
+        <v>-2.212095653970586</v>
       </c>
       <c r="G70">
-        <v>-11.64064069221986</v>
+        <v>-9.493794947094505</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.598301584338893</v>
       </c>
       <c r="E71">
-        <v>-14.56001963327945</v>
+        <v>-12.95996485520127</v>
       </c>
       <c r="F71">
-        <v>-3.64163496037118</v>
+        <v>-2.618628554038083</v>
       </c>
       <c r="G71">
-        <v>-9.790664807783109</v>
+        <v>-8.128509413971372</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.469949839577034</v>
       </c>
       <c r="E72">
-        <v>-15.04589319498443</v>
+        <v>-15.20686233206108</v>
       </c>
       <c r="F72">
-        <v>-3.793605587353971</v>
+        <v>-2.510317859387242</v>
       </c>
       <c r="G72">
-        <v>-9.960161428848256</v>
+        <v>-8.680536261553764</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.309613450412117</v>
       </c>
       <c r="E73">
-        <v>-14.55932224828227</v>
+        <v>-14.13523518593795</v>
       </c>
       <c r="F73">
-        <v>-3.407564011729526</v>
+        <v>-2.22981526108387</v>
       </c>
       <c r="G73">
-        <v>-11.04888067707514</v>
+        <v>-8.957287937000217</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.117597324521737</v>
       </c>
       <c r="E74">
-        <v>-13.55657319181581</v>
+        <v>-13.57330137480014</v>
       </c>
       <c r="F74">
-        <v>-3.731066333544817</v>
+        <v>-2.867457696328012</v>
       </c>
       <c r="G74">
-        <v>-9.800305116393467</v>
+        <v>-7.538391429414125</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.890990003529036</v>
       </c>
       <c r="E75">
-        <v>-16.29682074096726</v>
+        <v>-14.77187070430628</v>
       </c>
       <c r="F75">
-        <v>-3.299901100387674</v>
+        <v>-2.378075630469523</v>
       </c>
       <c r="G75">
-        <v>-9.530681045493065</v>
+        <v>-8.150832422542678</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.628830122635426</v>
       </c>
       <c r="E76">
-        <v>-14.04755487220143</v>
+        <v>-13.9674778663238</v>
       </c>
       <c r="F76">
-        <v>-3.752757962354525</v>
+        <v>-2.626070606784833</v>
       </c>
       <c r="G76">
-        <v>-9.267274179115415</v>
+        <v>-8.187013374741372</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.335360630133573</v>
       </c>
       <c r="E77">
-        <v>-15.92493792698336</v>
+        <v>-14.58691424041101</v>
       </c>
       <c r="F77">
-        <v>-4.436289466611551</v>
+        <v>-2.967316558368089</v>
       </c>
       <c r="G77">
-        <v>-9.431265362948752</v>
+        <v>-8.408210785493315</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.01272700900296</v>
       </c>
       <c r="E78">
-        <v>-16.04024193216666</v>
+        <v>-15.31995644192864</v>
       </c>
       <c r="F78">
-        <v>-4.082280858453363</v>
+        <v>-3.234341619027913</v>
       </c>
       <c r="G78">
-        <v>-9.600460724369823</v>
+        <v>-7.610928792725097</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.66698469889625</v>
       </c>
       <c r="E79">
-        <v>-16.10194239052117</v>
+        <v>-15.86251744126163</v>
       </c>
       <c r="F79">
-        <v>-3.590133702204329</v>
+        <v>-3.402047084826882</v>
       </c>
       <c r="G79">
-        <v>-8.794918920481123</v>
+        <v>-7.474815712877962</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.306777874039695</v>
       </c>
       <c r="E80">
-        <v>-16.46456900363339</v>
+        <v>-16.22061105189217</v>
       </c>
       <c r="F80">
-        <v>-4.459453932663436</v>
+        <v>-2.54369775225045</v>
       </c>
       <c r="G80">
-        <v>-8.634794453837653</v>
+        <v>-7.340917387996599</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.9380864565954453</v>
       </c>
       <c r="E81">
-        <v>-16.64249727586876</v>
+        <v>-16.65310749046873</v>
       </c>
       <c r="F81">
-        <v>-4.013876763432388</v>
+        <v>-2.994017324862526</v>
       </c>
       <c r="G81">
-        <v>-8.235003042878647</v>
+        <v>-6.63643660778523</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.5717109587006347</v>
       </c>
       <c r="E82">
-        <v>-18.04322221355132</v>
+        <v>-18.39800098120825</v>
       </c>
       <c r="F82">
-        <v>-4.370376272370795</v>
+        <v>-3.216766976210119</v>
       </c>
       <c r="G82">
-        <v>-7.372377502256294</v>
+        <v>-5.881612361558163</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.2175129332866796</v>
       </c>
       <c r="E83">
-        <v>-19.39929639751825</v>
+        <v>-19.37398675628938</v>
       </c>
       <c r="F83">
-        <v>-4.786803192697328</v>
+        <v>-3.375789494892943</v>
       </c>
       <c r="G83">
-        <v>-7.829434729953613</v>
+        <v>-5.618374333003016</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.1175335914157631</v>
       </c>
       <c r="E84">
-        <v>-19.9102486482777</v>
+        <v>-19.23925106913916</v>
       </c>
       <c r="F84">
-        <v>-3.893148841413582</v>
+        <v>-3.510519311121268</v>
       </c>
       <c r="G84">
-        <v>-8.300475702008814</v>
+        <v>-5.847487258139356</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.4212375930720215</v>
       </c>
       <c r="E85">
-        <v>-20.56257532908262</v>
+        <v>-20.24056459934519</v>
       </c>
       <c r="F85">
-        <v>-4.683884341471309</v>
+        <v>-3.446652184365426</v>
       </c>
       <c r="G85">
-        <v>-7.555424186213676</v>
+        <v>-5.465963437466049</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.6854377544958435</v>
       </c>
       <c r="E86">
-        <v>-21.26720135620211</v>
+        <v>-21.27350499202079</v>
       </c>
       <c r="F86">
-        <v>-4.165168957512287</v>
+        <v>-3.393374906486973</v>
       </c>
       <c r="G86">
-        <v>-8.178713837074419</v>
+        <v>-4.850155619524058</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.9014070283800938</v>
       </c>
       <c r="E87">
-        <v>-23.71755864175255</v>
+        <v>-22.41940364034372</v>
       </c>
       <c r="F87">
-        <v>-4.501451331617968</v>
+        <v>-3.85984764345364</v>
       </c>
       <c r="G87">
-        <v>-6.726701942458998</v>
+        <v>-4.563949026017446</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.059660442849099</v>
       </c>
       <c r="E88">
-        <v>-23.61635177615512</v>
+        <v>-22.9270048203375</v>
       </c>
       <c r="F88">
-        <v>-5.04417280291012</v>
+        <v>-3.789882075878388</v>
       </c>
       <c r="G88">
-        <v>-7.687266662315151</v>
+        <v>-4.944178423384899</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.154601274067362</v>
       </c>
       <c r="E89">
-        <v>-24.93160629541691</v>
+        <v>-24.32552891965233</v>
       </c>
       <c r="F89">
-        <v>-5.289405173937094</v>
+        <v>-4.045102901048318</v>
       </c>
       <c r="G89">
-        <v>-7.27963919006469</v>
+        <v>-4.911215321450375</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.179184540233801</v>
       </c>
       <c r="E90">
-        <v>-28.80598751741936</v>
+        <v>-24.94736085648959</v>
       </c>
       <c r="F90">
-        <v>-4.744189488395113</v>
+        <v>-4.127282745977848</v>
       </c>
       <c r="G90">
-        <v>-7.367901644687199</v>
+        <v>-5.723490774965954</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.130469259940377</v>
       </c>
       <c r="E91">
-        <v>-27.7659872337658</v>
+        <v>-26.43261428999933</v>
       </c>
       <c r="F91">
-        <v>-6.053453989746233</v>
+        <v>-3.958205503759844</v>
       </c>
       <c r="G91">
-        <v>-6.498856956264198</v>
+        <v>-4.816785320488204</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.007698242096341</v>
       </c>
       <c r="E92">
-        <v>-29.06390222605222</v>
+        <v>-28.53767543246489</v>
       </c>
       <c r="F92">
-        <v>-5.514673062189198</v>
+        <v>-4.081537812893052</v>
       </c>
       <c r="G92">
-        <v>-7.494649191203735</v>
+        <v>-4.765935341004999</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.8102241573260897</v>
       </c>
       <c r="E93">
-        <v>-30.97509939624942</v>
+        <v>-29.01209648340447</v>
       </c>
       <c r="F93">
-        <v>-5.206226317919787</v>
+        <v>-4.290910987420237</v>
       </c>
       <c r="G93">
-        <v>-7.715167940120129</v>
+        <v>-5.802573086808064</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.5447193575201937</v>
       </c>
       <c r="E94">
-        <v>-32.79207940048003</v>
+        <v>-32.08744431641251</v>
       </c>
       <c r="F94">
-        <v>-6.019621808281095</v>
+        <v>-4.667861230798958</v>
       </c>
       <c r="G94">
-        <v>-7.743221503019912</v>
+        <v>-6.018433898150702</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.2166469886878539</v>
       </c>
       <c r="E95">
-        <v>-34.90121390531549</v>
+        <v>-33.22161648129258</v>
       </c>
       <c r="F95">
-        <v>-5.755916015804289</v>
+        <v>-5.154117866446684</v>
       </c>
       <c r="G95">
-        <v>-7.806323811543961</v>
+        <v>-6.33209484581449</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.1692371514508068</v>
       </c>
       <c r="E96">
-        <v>-36.81395754938631</v>
+        <v>-34.8970839370205</v>
       </c>
       <c r="F96">
-        <v>-5.885573738425274</v>
+        <v>-4.790381739877422</v>
       </c>
       <c r="G96">
-        <v>-8.213994320886432</v>
+        <v>-6.15794359772113</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.595849176611153</v>
       </c>
       <c r="E97">
-        <v>-37.61846133498198</v>
+        <v>-38.26731467622302</v>
       </c>
       <c r="F97">
-        <v>-6.83510561286486</v>
+        <v>-5.086424510657312</v>
       </c>
       <c r="G97">
-        <v>-10.06964116983195</v>
+        <v>-6.853353483154896</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.06516329270714</v>
       </c>
       <c r="E98">
-        <v>-40.14251953500725</v>
+        <v>-40.01618190290426</v>
       </c>
       <c r="F98">
-        <v>-6.474057538517681</v>
+        <v>-5.636704006132607</v>
       </c>
       <c r="G98">
-        <v>-9.06074579564798</v>
+        <v>-7.014421455277057</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.54877784970511</v>
       </c>
       <c r="E99">
-        <v>-42.59213415082042</v>
+        <v>-41.83109239451336</v>
       </c>
       <c r="F99">
-        <v>-7.386630972913966</v>
+        <v>-5.72453911532105</v>
       </c>
       <c r="G99">
-        <v>-8.845553714504275</v>
+        <v>-6.632795007692032</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.06106117980704</v>
       </c>
       <c r="E100">
-        <v>-44.97257406192942</v>
+        <v>-44.00369572680333</v>
       </c>
       <c r="F100">
-        <v>-6.768897105645006</v>
+        <v>-5.676087077563904</v>
       </c>
       <c r="G100">
-        <v>-10.85061541527372</v>
+        <v>-7.920491285011266</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.551714834725315</v>
       </c>
       <c r="E101">
-        <v>-48.44176214726605</v>
+        <v>-45.9734415374457</v>
       </c>
       <c r="F101">
-        <v>-7.212956705794126</v>
+        <v>-5.898184803765493</v>
       </c>
       <c r="G101">
-        <v>-8.602235238458922</v>
+        <v>-7.793717254130416</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.077131129766694</v>
       </c>
       <c r="E102">
-        <v>-48.78901232688523</v>
+        <v>-48.6847894975987</v>
       </c>
       <c r="F102">
-        <v>-7.199592654484761</v>
+        <v>-6.091867871316254</v>
       </c>
       <c r="G102">
-        <v>-11.35938667484</v>
+        <v>-8.648758334922299</v>
       </c>
     </row>
   </sheetData>
